--- a/evaluation/function_inventory.xlsx
+++ b/evaluation/function_inventory.xlsx
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabriela/Dropbox/PERSONAL/LLC/Oikobit LLC/projects/forestgeo-ctfs-review/fgeo2/registry/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabriela/Dropbox/PERSONAL/LLC/Oikobit LLC/projects/code-and-statistics-forestgeo/fgeo2/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C93E29-9E67-924B-9D5A-2F304CCAE146}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D2ADA9-2791-8249-80EC-CFD5BE41BDD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8200" yWindow="2240" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3460" yWindow="980" windowWidth="31940" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="functions" sheetId="1" r:id="rId1"/>
     <sheet name="modules" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">functions!$A$1:$H$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">functions!$A$1:$G$372</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="766">
   <si>
     <t>abund.manycensus</t>
   </si>
@@ -2273,9 +2273,6 @@
     <t>status</t>
   </si>
   <si>
-    <t>decision</t>
-  </si>
-  <si>
     <t>replacement</t>
   </si>
   <si>
@@ -2304,6 +2301,27 @@
   </si>
   <si>
     <t>08_QAQC</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
+  </si>
+  <si>
+    <t>se.skewness</t>
+  </si>
+  <si>
+    <t>se.kurtosis</t>
+  </si>
+  <si>
+    <t>deprecated</t>
+  </si>
+  <si>
+    <t>neighborhoods.R</t>
+  </si>
+  <si>
+    <t>See neighborhoods.qmd. The old functions to count neighbors and do Ripley's K have been substituted by auxiliary functions + tutorials to implement more flexible analyses of neighborhoods</t>
+  </si>
+  <si>
+    <t>not evaluated</t>
   </si>
 </sst>
 </file>
@@ -3144,18 +3162,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H372"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G372"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="21.33203125" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="38.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="65.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>744</v>
       </c>
@@ -3177,16 +3197,13 @@
       <c r="G1" t="s">
         <v>750</v>
       </c>
-      <c r="H1" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -3194,13 +3211,16 @@
       <c r="D2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C3" t="s">
         <v>109</v>
@@ -3208,13 +3228,16 @@
       <c r="D3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
@@ -3222,13 +3245,16 @@
       <c r="D4" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>595</v>
       </c>
       <c r="B5" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C5" t="s">
         <v>109</v>
@@ -3236,13 +3262,16 @@
       <c r="D5" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -3250,13 +3279,16 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -3264,13 +3296,16 @@
       <c r="D7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -3278,13 +3313,16 @@
       <c r="D8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E8" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -3292,13 +3330,16 @@
       <c r="D9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
@@ -3306,13 +3347,16 @@
       <c r="D10" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E10" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -3320,13 +3364,16 @@
       <c r="D11" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -3334,13 +3381,16 @@
       <c r="D12" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E12" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -3348,13 +3398,16 @@
       <c r="D13" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>128</v>
       </c>
       <c r="B14" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -3362,13 +3415,16 @@
       <c r="D14" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E14" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>152</v>
       </c>
       <c r="B15" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
@@ -3376,13 +3432,16 @@
       <c r="D15" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E15" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>154</v>
       </c>
       <c r="B16" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -3390,13 +3449,16 @@
       <c r="D16" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -3404,13 +3466,16 @@
       <c r="D17" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>196</v>
       </c>
       <c r="B18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
@@ -3418,13 +3483,16 @@
       <c r="D18" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>196</v>
       </c>
       <c r="B19" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -3432,13 +3500,16 @@
       <c r="D19" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>199</v>
       </c>
       <c r="B20" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -3446,13 +3517,16 @@
       <c r="D20" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>201</v>
       </c>
       <c r="B21" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
@@ -3460,13 +3534,16 @@
       <c r="D21" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>205</v>
       </c>
       <c r="B22" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
@@ -3474,13 +3551,16 @@
       <c r="D22" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>207</v>
       </c>
       <c r="B23" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -3488,13 +3568,16 @@
       <c r="D23" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>219</v>
       </c>
       <c r="B24" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -3502,13 +3585,16 @@
       <c r="D24" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -3516,13 +3602,16 @@
       <c r="D25" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>223</v>
       </c>
       <c r="B26" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -3530,13 +3619,16 @@
       <c r="D26" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>225</v>
       </c>
       <c r="B27" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -3544,13 +3636,16 @@
       <c r="D27" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -3558,13 +3653,16 @@
       <c r="D28" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>229</v>
       </c>
       <c r="B29" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
@@ -3572,13 +3670,16 @@
       <c r="D29" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>231</v>
       </c>
       <c r="B30" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
@@ -3586,13 +3687,16 @@
       <c r="D30" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>233</v>
       </c>
       <c r="B31" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
@@ -3600,13 +3704,16 @@
       <c r="D31" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>235</v>
       </c>
       <c r="B32" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
@@ -3614,13 +3721,16 @@
       <c r="D32" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>244</v>
       </c>
       <c r="B33" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
@@ -3628,13 +3738,16 @@
       <c r="D33" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>246</v>
       </c>
       <c r="B34" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -3642,13 +3755,16 @@
       <c r="D34" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>248</v>
       </c>
       <c r="B35" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -3656,13 +3772,16 @@
       <c r="D35" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>250</v>
       </c>
       <c r="B36" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -3670,13 +3789,16 @@
       <c r="D36" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>252</v>
       </c>
       <c r="B37" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -3684,13 +3806,16 @@
       <c r="D37" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>254</v>
       </c>
       <c r="B38" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -3698,13 +3823,16 @@
       <c r="D38" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>256</v>
       </c>
       <c r="B39" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -3712,13 +3840,16 @@
       <c r="D39" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>258</v>
       </c>
       <c r="B40" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C40" t="s">
         <v>13</v>
@@ -3726,13 +3857,16 @@
       <c r="D40" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>266</v>
       </c>
       <c r="B41" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
@@ -3740,13 +3874,16 @@
       <c r="D41" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>268</v>
       </c>
       <c r="B42" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
@@ -3754,13 +3891,16 @@
       <c r="D42" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>278</v>
       </c>
       <c r="B43" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -3768,13 +3908,16 @@
       <c r="D43" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>282</v>
       </c>
       <c r="B44" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -3782,13 +3925,16 @@
       <c r="D44" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>284</v>
       </c>
       <c r="B45" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -3796,13 +3942,16 @@
       <c r="D45" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>303</v>
       </c>
       <c r="B46" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -3810,13 +3959,16 @@
       <c r="D46" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>305</v>
       </c>
       <c r="B47" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -3824,13 +3976,16 @@
       <c r="D47" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>307</v>
       </c>
       <c r="B48" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
@@ -3838,13 +3993,16 @@
       <c r="D48" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>309</v>
       </c>
       <c r="B49" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
@@ -3852,13 +4010,16 @@
       <c r="D49" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>352</v>
       </c>
       <c r="B50" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
@@ -3866,13 +4027,16 @@
       <c r="D50" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>416</v>
       </c>
       <c r="B51" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
@@ -3880,13 +4044,16 @@
       <c r="D51" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E51" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>431</v>
       </c>
       <c r="B52" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
@@ -3894,13 +4061,16 @@
       <c r="D52" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E52" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>433</v>
       </c>
       <c r="B53" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
@@ -3908,13 +4078,16 @@
       <c r="D53" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>434</v>
       </c>
       <c r="B54" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
@@ -3922,13 +4095,16 @@
       <c r="D54" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>435</v>
       </c>
       <c r="B55" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -3936,13 +4112,16 @@
       <c r="D55" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>437</v>
       </c>
       <c r="B56" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -3950,13 +4129,16 @@
       <c r="D56" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E56" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>457</v>
       </c>
       <c r="B57" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -3964,13 +4146,16 @@
       <c r="D57" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E57" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>461</v>
       </c>
       <c r="B58" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -3978,13 +4163,16 @@
       <c r="D58" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>463</v>
       </c>
       <c r="B59" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
@@ -3992,13 +4180,16 @@
       <c r="D59" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E59" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>465</v>
       </c>
       <c r="B60" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
@@ -4006,13 +4197,16 @@
       <c r="D60" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E60" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>467</v>
       </c>
       <c r="B61" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -4020,13 +4214,16 @@
       <c r="D61" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E61" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>469</v>
       </c>
       <c r="B62" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C62" t="s">
         <v>13</v>
@@ -4034,13 +4231,16 @@
       <c r="D62" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E62" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>470</v>
       </c>
       <c r="B63" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
@@ -4048,13 +4248,16 @@
       <c r="D63" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E63" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>472</v>
       </c>
       <c r="B64" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
@@ -4062,13 +4265,16 @@
       <c r="D64" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E64" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>474</v>
       </c>
       <c r="B65" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
@@ -4076,13 +4282,16 @@
       <c r="D65" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>476</v>
       </c>
       <c r="B66" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
@@ -4090,13 +4299,16 @@
       <c r="D66" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>477</v>
       </c>
       <c r="B67" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
@@ -4104,13 +4316,16 @@
       <c r="D67" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E67" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>507</v>
       </c>
       <c r="B68" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
@@ -4118,13 +4333,16 @@
       <c r="D68" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E68" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>509</v>
       </c>
       <c r="B69" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
@@ -4132,13 +4350,16 @@
       <c r="D69" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E69" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>511</v>
       </c>
       <c r="B70" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
@@ -4146,13 +4367,16 @@
       <c r="D70" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E70" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>530</v>
       </c>
       <c r="B71" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
@@ -4160,13 +4384,16 @@
       <c r="D71" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>541</v>
       </c>
       <c r="B72" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
@@ -4174,13 +4401,16 @@
       <c r="D72" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E72" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>558</v>
       </c>
       <c r="B73" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C73" t="s">
         <v>13</v>
@@ -4188,13 +4418,16 @@
       <c r="D73" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>570</v>
       </c>
       <c r="B74" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
@@ -4202,13 +4435,16 @@
       <c r="D74" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>578</v>
       </c>
       <c r="B75" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C75" t="s">
         <v>13</v>
@@ -4216,13 +4452,16 @@
       <c r="D75" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E75" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>582</v>
       </c>
       <c r="B76" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C76" t="s">
         <v>13</v>
@@ -4230,13 +4469,16 @@
       <c r="D76" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E76" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>584</v>
       </c>
       <c r="B77" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
@@ -4244,13 +4486,16 @@
       <c r="D77" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E77" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>586</v>
       </c>
       <c r="B78" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
@@ -4258,13 +4503,16 @@
       <c r="D78" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E78" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>599</v>
       </c>
       <c r="B79" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C79" t="s">
         <v>13</v>
@@ -4272,13 +4520,16 @@
       <c r="D79" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E79" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>631</v>
       </c>
       <c r="B80" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C80" t="s">
         <v>13</v>
@@ -4286,13 +4537,16 @@
       <c r="D80" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E80" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>639</v>
       </c>
       <c r="B81" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C81" t="s">
         <v>13</v>
@@ -4300,13 +4554,16 @@
       <c r="D81" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E81" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>644</v>
       </c>
       <c r="B82" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C82" t="s">
         <v>13</v>
@@ -4314,13 +4571,16 @@
       <c r="D82" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>646</v>
       </c>
       <c r="B83" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
@@ -4328,13 +4588,16 @@
       <c r="D83" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E83" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>648</v>
       </c>
       <c r="B84" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C84" t="s">
         <v>13</v>
@@ -4342,13 +4605,16 @@
       <c r="D84" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E84" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>650</v>
       </c>
       <c r="B85" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
@@ -4356,13 +4622,16 @@
       <c r="D85" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E85" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>671</v>
       </c>
       <c r="B86" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
@@ -4370,13 +4639,16 @@
       <c r="D86" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E86" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>673</v>
       </c>
       <c r="B87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C87" t="s">
         <v>13</v>
@@ -4384,13 +4656,16 @@
       <c r="D87" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E87" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>723</v>
       </c>
       <c r="B88" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C88" t="s">
         <v>13</v>
@@ -4398,13 +4673,16 @@
       <c r="D88" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E88" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>725</v>
       </c>
       <c r="B89" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C89" t="s">
         <v>13</v>
@@ -4412,13 +4690,16 @@
       <c r="D89" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E89" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>727</v>
       </c>
       <c r="B90" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C90" t="s">
         <v>13</v>
@@ -4426,13 +4707,16 @@
       <c r="D90" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E90" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>29</v>
       </c>
       <c r="B91" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C91" t="s">
         <v>30</v>
@@ -4440,13 +4724,16 @@
       <c r="D91" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E91" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>35</v>
       </c>
       <c r="B92" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C92" t="s">
         <v>30</v>
@@ -4454,13 +4741,16 @@
       <c r="D92" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E92" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>126</v>
       </c>
       <c r="B93" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C93" t="s">
         <v>30</v>
@@ -4468,13 +4758,16 @@
       <c r="D93" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E93" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>136</v>
       </c>
       <c r="B94" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C94" t="s">
         <v>30</v>
@@ -4482,13 +4775,16 @@
       <c r="D94" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E94" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>262</v>
       </c>
       <c r="B95" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C95" t="s">
         <v>30</v>
@@ -4496,13 +4792,16 @@
       <c r="D95" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E95" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>272</v>
       </c>
       <c r="B96" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C96" t="s">
         <v>30</v>
@@ -4510,13 +4809,16 @@
       <c r="D96" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E96" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>321</v>
       </c>
       <c r="B97" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C97" t="s">
         <v>30</v>
@@ -4524,13 +4826,16 @@
       <c r="D97" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E97" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>323</v>
       </c>
       <c r="B98" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C98" t="s">
         <v>30</v>
@@ -4538,13 +4843,16 @@
       <c r="D98" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E98" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>408</v>
       </c>
       <c r="B99" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C99" t="s">
         <v>30</v>
@@ -4552,13 +4860,16 @@
       <c r="D99" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E99" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>410</v>
       </c>
       <c r="B100" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C100" t="s">
         <v>30</v>
@@ -4566,13 +4877,16 @@
       <c r="D100" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E100" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>412</v>
       </c>
       <c r="B101" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C101" t="s">
         <v>30</v>
@@ -4580,13 +4894,16 @@
       <c r="D101" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E101" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>414</v>
       </c>
       <c r="B102" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C102" t="s">
         <v>30</v>
@@ -4594,13 +4911,16 @@
       <c r="D102" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E102" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>418</v>
       </c>
       <c r="B103" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C103" t="s">
         <v>30</v>
@@ -4608,13 +4928,16 @@
       <c r="D103" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E103" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>424</v>
       </c>
       <c r="B104" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C104" t="s">
         <v>30</v>
@@ -4622,13 +4945,16 @@
       <c r="D104" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E104" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>430</v>
       </c>
       <c r="B105" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C105" t="s">
         <v>30</v>
@@ -4636,13 +4962,16 @@
       <c r="D105" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E105" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>549</v>
       </c>
       <c r="B106" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C106" t="s">
         <v>30</v>
@@ -4650,13 +4979,16 @@
       <c r="D106" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E106" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>555</v>
       </c>
       <c r="B107" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C107" t="s">
         <v>30</v>
@@ -4664,13 +4996,16 @@
       <c r="D107" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E107" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>557</v>
       </c>
       <c r="B108" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C108" t="s">
         <v>30</v>
@@ -4678,13 +5013,16 @@
       <c r="D108" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E108" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>565</v>
       </c>
       <c r="B109" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C109" t="s">
         <v>30</v>
@@ -4692,13 +5030,16 @@
       <c r="D109" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E109" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>580</v>
       </c>
       <c r="B110" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C110" t="s">
         <v>30</v>
@@ -4706,13 +5047,16 @@
       <c r="D110" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E110" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>662</v>
       </c>
       <c r="B111" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C111" t="s">
         <v>30</v>
@@ -4720,13 +5064,16 @@
       <c r="D111" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E111" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>680</v>
       </c>
       <c r="B112" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C112" t="s">
         <v>30</v>
@@ -4734,13 +5081,16 @@
       <c r="D112" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E112" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>739</v>
       </c>
       <c r="B113" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C113" t="s">
         <v>30</v>
@@ -4748,13 +5098,16 @@
       <c r="D113" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E113" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>741</v>
       </c>
       <c r="B114" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C114" t="s">
         <v>30</v>
@@ -4762,13 +5115,16 @@
       <c r="D114" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E114" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>743</v>
       </c>
       <c r="B115" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C115" t="s">
         <v>30</v>
@@ -4776,13 +5132,16 @@
       <c r="D115" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E115" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>37</v>
       </c>
       <c r="B116" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C116" t="s">
         <v>38</v>
@@ -4790,13 +5149,16 @@
       <c r="D116" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E116" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C117" t="s">
         <v>38</v>
@@ -4804,13 +5166,16 @@
       <c r="D117" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E117" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>75</v>
       </c>
       <c r="B118" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C118" t="s">
         <v>38</v>
@@ -4818,13 +5183,16 @@
       <c r="D118" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E118" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>182</v>
       </c>
       <c r="B119" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C119" t="s">
         <v>38</v>
@@ -4832,13 +5200,16 @@
       <c r="D119" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E119" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>317</v>
       </c>
       <c r="B120" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C120" t="s">
         <v>38</v>
@@ -4846,13 +5217,16 @@
       <c r="D120" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E120" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>445</v>
       </c>
       <c r="B121" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C121" t="s">
         <v>38</v>
@@ -4860,13 +5234,16 @@
       <c r="D121" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E121" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>445</v>
       </c>
       <c r="B122" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C122" t="s">
         <v>38</v>
@@ -4874,13 +5251,16 @@
       <c r="D122" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E122" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>447</v>
       </c>
       <c r="B123" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C123" t="s">
         <v>38</v>
@@ -4888,13 +5268,16 @@
       <c r="D123" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E123" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>449</v>
       </c>
       <c r="B124" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C124" t="s">
         <v>38</v>
@@ -4902,13 +5285,16 @@
       <c r="D124" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E124" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>451</v>
       </c>
       <c r="B125" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C125" t="s">
         <v>38</v>
@@ -4916,13 +5302,16 @@
       <c r="D125" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E125" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>605</v>
       </c>
       <c r="B126" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C126" t="s">
         <v>38</v>
@@ -4930,13 +5319,16 @@
       <c r="D126" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E126" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>624</v>
       </c>
       <c r="B127" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C127" t="s">
         <v>38</v>
@@ -4944,13 +5336,16 @@
       <c r="D127" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E127" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>626</v>
       </c>
       <c r="B128" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C128" t="s">
         <v>38</v>
@@ -4958,13 +5353,16 @@
       <c r="D128" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E128" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>629</v>
       </c>
       <c r="B129" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C129" t="s">
         <v>38</v>
@@ -4972,13 +5370,16 @@
       <c r="D129" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E129" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>658</v>
       </c>
       <c r="B130" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C130" t="s">
         <v>38</v>
@@ -4986,13 +5387,16 @@
       <c r="D130" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E130" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>697</v>
       </c>
       <c r="B131" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C131" t="s">
         <v>38</v>
@@ -5000,13 +5404,16 @@
       <c r="D131" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E131" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>519</v>
       </c>
       <c r="B132" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C132" t="s">
         <v>520</v>
@@ -5014,13 +5421,16 @@
       <c r="D132" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E132" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>628</v>
       </c>
       <c r="B133" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C133" t="s">
         <v>520</v>
@@ -5028,13 +5438,16 @@
       <c r="D133" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E133" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>699</v>
       </c>
       <c r="B134" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C134" t="s">
         <v>520</v>
@@ -5042,13 +5455,16 @@
       <c r="D134" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E134" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>40</v>
       </c>
       <c r="B135" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C135" t="s">
         <v>41</v>
@@ -5056,13 +5472,16 @@
       <c r="D135" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E135" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>59</v>
       </c>
       <c r="B136" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C136" t="s">
         <v>41</v>
@@ -5070,13 +5489,16 @@
       <c r="D136" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E136" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>73</v>
       </c>
       <c r="B137" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C137" t="s">
         <v>41</v>
@@ -5084,13 +5506,16 @@
       <c r="D137" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E137" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>98</v>
       </c>
       <c r="B138" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C138" t="s">
         <v>41</v>
@@ -5098,13 +5523,16 @@
       <c r="D138" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E138" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>100</v>
       </c>
       <c r="B139" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C139" t="s">
         <v>41</v>
@@ -5112,13 +5540,16 @@
       <c r="D139" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E139" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>102</v>
       </c>
       <c r="B140" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C140" t="s">
         <v>41</v>
@@ -5126,13 +5557,16 @@
       <c r="D140" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E140" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>134</v>
       </c>
       <c r="B141" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C141" t="s">
         <v>41</v>
@@ -5140,13 +5574,16 @@
       <c r="D141" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E141" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C142" t="s">
         <v>41</v>
@@ -5154,13 +5591,16 @@
       <c r="D142" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E142" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>192</v>
       </c>
       <c r="B143" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C143" t="s">
         <v>41</v>
@@ -5168,13 +5608,16 @@
       <c r="D143" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E143" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>336</v>
       </c>
       <c r="B144" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C144" t="s">
         <v>41</v>
@@ -5182,13 +5625,16 @@
       <c r="D144" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E144" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>338</v>
       </c>
       <c r="B145" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C145" t="s">
         <v>41</v>
@@ -5196,13 +5642,16 @@
       <c r="D145" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E145" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>340</v>
       </c>
       <c r="B146" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C146" t="s">
         <v>41</v>
@@ -5210,13 +5659,16 @@
       <c r="D146" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E146" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>342</v>
       </c>
       <c r="B147" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C147" t="s">
         <v>41</v>
@@ -5224,13 +5676,16 @@
       <c r="D147" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E147" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>350</v>
       </c>
       <c r="B148" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C148" t="s">
         <v>41</v>
@@ -5238,13 +5693,16 @@
       <c r="D148" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E148" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>385</v>
       </c>
       <c r="B149" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C149" t="s">
         <v>41</v>
@@ -5252,13 +5710,16 @@
       <c r="D149" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E149" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>387</v>
       </c>
       <c r="B150" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C150" t="s">
         <v>41</v>
@@ -5266,13 +5727,16 @@
       <c r="D150" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E150" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>422</v>
       </c>
       <c r="B151" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C151" t="s">
         <v>41</v>
@@ -5280,13 +5744,16 @@
       <c r="D151" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E151" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>439</v>
       </c>
       <c r="B152" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C152" t="s">
         <v>41</v>
@@ -5294,13 +5761,16 @@
       <c r="D152" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E152" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>441</v>
       </c>
       <c r="B153" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C153" t="s">
         <v>41</v>
@@ -5308,13 +5778,16 @@
       <c r="D153" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E153" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>481</v>
       </c>
       <c r="B154" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C154" t="s">
         <v>41</v>
@@ -5322,13 +5795,16 @@
       <c r="D154" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E154" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>483</v>
       </c>
       <c r="B155" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C155" t="s">
         <v>41</v>
@@ -5336,13 +5812,16 @@
       <c r="D155" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E155" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>501</v>
       </c>
       <c r="B156" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C156" t="s">
         <v>41</v>
@@ -5350,13 +5829,16 @@
       <c r="D156" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E156" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>503</v>
       </c>
       <c r="B157" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C157" t="s">
         <v>41</v>
@@ -5364,13 +5846,16 @@
       <c r="D157" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E157" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>505</v>
       </c>
       <c r="B158" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C158" t="s">
         <v>41</v>
@@ -5378,13 +5863,16 @@
       <c r="D158" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E158" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>513</v>
       </c>
       <c r="B159" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C159" t="s">
         <v>41</v>
@@ -5392,13 +5880,16 @@
       <c r="D159" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E159" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>517</v>
       </c>
       <c r="B160" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C160" t="s">
         <v>41</v>
@@ -5406,13 +5897,16 @@
       <c r="D160" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E160" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>612</v>
       </c>
       <c r="B161" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C161" t="s">
         <v>41</v>
@@ -5420,13 +5914,16 @@
       <c r="D161" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E161" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>614</v>
       </c>
       <c r="B162" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C162" t="s">
         <v>41</v>
@@ -5434,13 +5931,16 @@
       <c r="D162" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E162" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>616</v>
       </c>
       <c r="B163" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C163" t="s">
         <v>41</v>
@@ -5448,13 +5948,16 @@
       <c r="D163" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E163" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>618</v>
       </c>
       <c r="B164" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C164" t="s">
         <v>41</v>
@@ -5462,13 +5965,16 @@
       <c r="D164" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E164" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>620</v>
       </c>
       <c r="B165" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C165" t="s">
         <v>41</v>
@@ -5476,13 +5982,16 @@
       <c r="D165" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E165" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>622</v>
       </c>
       <c r="B166" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C166" t="s">
         <v>41</v>
@@ -5490,13 +5999,16 @@
       <c r="D166" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E166" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>675</v>
       </c>
       <c r="B167" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C167" t="s">
         <v>41</v>
@@ -5504,13 +6016,16 @@
       <c r="D167" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E167" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>675</v>
+        <v>760</v>
       </c>
       <c r="B168" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C168" t="s">
         <v>41</v>
@@ -5518,13 +6033,16 @@
       <c r="D168" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E168" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>675</v>
+        <v>759</v>
       </c>
       <c r="B169" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C169" t="s">
         <v>41</v>
@@ -5532,13 +6050,16 @@
       <c r="D169" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E169" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>675</v>
+        <v>761</v>
       </c>
       <c r="B170" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C170" t="s">
         <v>41</v>
@@ -5546,13 +6067,16 @@
       <c r="D170" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E170" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>690</v>
       </c>
       <c r="B171" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C171" t="s">
         <v>41</v>
@@ -5560,13 +6084,16 @@
       <c r="D171" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E171" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>700</v>
       </c>
       <c r="B172" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C172" t="s">
         <v>41</v>
@@ -5574,13 +6101,16 @@
       <c r="D172" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E172" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>702</v>
       </c>
       <c r="B173" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C173" t="s">
         <v>41</v>
@@ -5588,13 +6118,16 @@
       <c r="D173" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E173" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>56</v>
       </c>
       <c r="B174" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C174" t="s">
         <v>57</v>
@@ -5602,13 +6135,16 @@
       <c r="D174" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E174" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>130</v>
       </c>
       <c r="B175" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C175" t="s">
         <v>57</v>
@@ -5616,13 +6152,16 @@
       <c r="D175" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E175" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>158</v>
       </c>
       <c r="B176" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C176" t="s">
         <v>57</v>
@@ -5630,13 +6169,16 @@
       <c r="D176" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E176" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>163</v>
       </c>
       <c r="B177" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C177" t="s">
         <v>57</v>
@@ -5644,13 +6186,16 @@
       <c r="D177" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E177" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>165</v>
       </c>
       <c r="B178" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C178" t="s">
         <v>57</v>
@@ -5658,13 +6203,16 @@
       <c r="D178" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E178" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>167</v>
       </c>
       <c r="B179" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C179" t="s">
         <v>57</v>
@@ -5672,13 +6220,16 @@
       <c r="D179" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E179" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>169</v>
       </c>
       <c r="B180" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C180" t="s">
         <v>57</v>
@@ -5686,13 +6237,16 @@
       <c r="D180" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E180" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>171</v>
       </c>
       <c r="B181" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C181" t="s">
         <v>57</v>
@@ -5700,13 +6254,16 @@
       <c r="D181" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E181" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>175</v>
       </c>
       <c r="B182" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C182" t="s">
         <v>57</v>
@@ -5714,13 +6271,16 @@
       <c r="D182" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E182" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>177</v>
       </c>
       <c r="B183" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C183" t="s">
         <v>57</v>
@@ -5728,13 +6288,16 @@
       <c r="D183" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E183" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C184" t="s">
         <v>57</v>
@@ -5742,13 +6305,16 @@
       <c r="D184" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E184" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>186</v>
       </c>
       <c r="B185" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C185" t="s">
         <v>57</v>
@@ -5756,13 +6322,16 @@
       <c r="D185" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E185" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>217</v>
       </c>
       <c r="B186" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C186" t="s">
         <v>57</v>
@@ -5770,13 +6339,16 @@
       <c r="D186" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E186" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>242</v>
       </c>
       <c r="B187" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C187" t="s">
         <v>57</v>
@@ -5784,13 +6356,16 @@
       <c r="D187" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E187" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>264</v>
       </c>
       <c r="B188" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C188" t="s">
         <v>57</v>
@@ -5798,13 +6373,16 @@
       <c r="D188" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E188" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>280</v>
       </c>
       <c r="B189" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C189" t="s">
         <v>57</v>
@@ -5812,13 +6390,16 @@
       <c r="D189" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E189" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>288</v>
       </c>
       <c r="B190" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C190" t="s">
         <v>57</v>
@@ -5826,13 +6407,16 @@
       <c r="D190" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E190" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>290</v>
       </c>
       <c r="B191" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C191" t="s">
         <v>57</v>
@@ -5840,13 +6424,16 @@
       <c r="D191" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E191" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>295</v>
       </c>
       <c r="B192" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C192" t="s">
         <v>57</v>
@@ -5854,13 +6441,16 @@
       <c r="D192" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E192" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>313</v>
       </c>
       <c r="B193" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C193" t="s">
         <v>57</v>
@@ -5868,13 +6458,16 @@
       <c r="D193" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E193" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>360</v>
       </c>
       <c r="B194" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C194" t="s">
         <v>57</v>
@@ -5882,13 +6475,16 @@
       <c r="D194" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E194" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>374</v>
       </c>
       <c r="B195" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C195" t="s">
         <v>57</v>
@@ -5896,13 +6492,16 @@
       <c r="D195" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E195" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>393</v>
       </c>
       <c r="B196" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C196" t="s">
         <v>57</v>
@@ -5910,13 +6509,16 @@
       <c r="D196" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E196" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>420</v>
       </c>
       <c r="B197" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C197" t="s">
         <v>57</v>
@@ -5924,13 +6526,16 @@
       <c r="D197" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E197" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>426</v>
       </c>
       <c r="B198" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C198" t="s">
         <v>57</v>
@@ -5938,13 +6543,16 @@
       <c r="D198" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E198" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>428</v>
       </c>
       <c r="B199" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C199" t="s">
         <v>57</v>
@@ -5952,13 +6560,16 @@
       <c r="D199" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E199" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>459</v>
       </c>
       <c r="B200" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C200" t="s">
         <v>57</v>
@@ -5966,13 +6577,16 @@
       <c r="D200" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E200" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>485</v>
       </c>
       <c r="B201" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C201" t="s">
         <v>57</v>
@@ -5980,13 +6594,16 @@
       <c r="D201" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E201" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>495</v>
       </c>
       <c r="B202" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C202" t="s">
         <v>57</v>
@@ -5994,13 +6611,16 @@
       <c r="D202" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E202" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>497</v>
       </c>
       <c r="B203" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C203" t="s">
         <v>57</v>
@@ -6008,13 +6628,16 @@
       <c r="D203" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E203" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>499</v>
       </c>
       <c r="B204" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C204" t="s">
         <v>57</v>
@@ -6022,13 +6645,16 @@
       <c r="D204" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E204" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>539</v>
       </c>
       <c r="B205" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C205" t="s">
         <v>57</v>
@@ -6036,13 +6662,16 @@
       <c r="D205" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E205" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>543</v>
       </c>
       <c r="B206" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C206" t="s">
         <v>57</v>
@@ -6050,13 +6679,16 @@
       <c r="D206" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E206" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>545</v>
       </c>
       <c r="B207" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C207" t="s">
         <v>57</v>
@@ -6064,13 +6696,16 @@
       <c r="D207" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E207" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>576</v>
       </c>
       <c r="B208" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C208" t="s">
         <v>57</v>
@@ -6078,13 +6713,16 @@
       <c r="D208" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E208" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>592</v>
       </c>
       <c r="B209" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C209" t="s">
         <v>57</v>
@@ -6092,13 +6730,16 @@
       <c r="D209" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E209" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>592</v>
       </c>
       <c r="B210" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C210" t="s">
         <v>57</v>
@@ -6106,13 +6747,16 @@
       <c r="D210" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E210" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>633</v>
       </c>
       <c r="B211" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C211" t="s">
         <v>57</v>
@@ -6120,13 +6764,16 @@
       <c r="D211" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E211" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>635</v>
       </c>
       <c r="B212" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C212" t="s">
         <v>57</v>
@@ -6134,13 +6781,16 @@
       <c r="D212" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E212" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>656</v>
       </c>
       <c r="B213" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C213" t="s">
         <v>57</v>
@@ -6148,13 +6798,16 @@
       <c r="D213" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E213" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>684</v>
       </c>
       <c r="B214" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C214" t="s">
         <v>57</v>
@@ -6162,13 +6815,16 @@
       <c r="D214" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E214" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>695</v>
       </c>
       <c r="B215" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C215" t="s">
         <v>57</v>
@@ -6176,13 +6832,16 @@
       <c r="D215" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E215" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>704</v>
       </c>
       <c r="B216" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C216" t="s">
         <v>57</v>
@@ -6190,13 +6849,16 @@
       <c r="D216" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E216" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>706</v>
       </c>
       <c r="B217" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C217" t="s">
         <v>57</v>
@@ -6204,13 +6866,16 @@
       <c r="D217" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E217" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>710</v>
       </c>
       <c r="B218" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C218" t="s">
         <v>57</v>
@@ -6218,13 +6883,16 @@
       <c r="D218" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E218" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>716</v>
       </c>
       <c r="B219" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C219" t="s">
         <v>57</v>
@@ -6232,13 +6900,16 @@
       <c r="D219" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E219" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>729</v>
       </c>
       <c r="B220" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C220" t="s">
         <v>57</v>
@@ -6246,13 +6917,16 @@
       <c r="D220" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E220" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>731</v>
       </c>
       <c r="B221" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C221" t="s">
         <v>57</v>
@@ -6260,13 +6934,16 @@
       <c r="D221" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E221" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>733</v>
       </c>
       <c r="B222" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C222" t="s">
         <v>57</v>
@@ -6274,13 +6951,16 @@
       <c r="D222" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E222" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>735</v>
       </c>
       <c r="B223" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C223" t="s">
         <v>57</v>
@@ -6288,13 +6968,16 @@
       <c r="D223" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E223" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>44</v>
       </c>
       <c r="B224" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C224" t="s">
         <v>45</v>
@@ -6302,13 +6985,16 @@
       <c r="D224" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E224" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>140</v>
       </c>
       <c r="B225" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C225" t="s">
         <v>45</v>
@@ -6316,13 +7002,16 @@
       <c r="D225" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E225" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>173</v>
       </c>
       <c r="B226" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C226" t="s">
         <v>45</v>
@@ -6330,13 +7019,16 @@
       <c r="D226" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E226" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>190</v>
       </c>
       <c r="B227" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C227" t="s">
         <v>45</v>
@@ -6344,13 +7036,16 @@
       <c r="D227" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E227" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>276</v>
       </c>
       <c r="B228" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C228" t="s">
         <v>45</v>
@@ -6358,13 +7053,16 @@
       <c r="D228" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E228" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>455</v>
       </c>
       <c r="B229" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C229" t="s">
         <v>45</v>
@@ -6372,13 +7070,16 @@
       <c r="D229" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E229" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>641</v>
       </c>
       <c r="B230" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C230" t="s">
         <v>45</v>
@@ -6386,13 +7087,16 @@
       <c r="D230" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E230" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>714</v>
       </c>
       <c r="B231" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C231" t="s">
         <v>45</v>
@@ -6400,13 +7104,16 @@
       <c r="D231" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E231" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>15</v>
       </c>
       <c r="B232" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C232" t="s">
         <v>16</v>
@@ -6414,13 +7121,16 @@
       <c r="D232" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E232" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>18</v>
       </c>
       <c r="B233" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C233" t="s">
         <v>16</v>
@@ -6428,13 +7138,16 @@
       <c r="D233" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E233" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>20</v>
       </c>
       <c r="B234" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C234" t="s">
         <v>16</v>
@@ -6442,13 +7155,16 @@
       <c r="D234" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E234" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>22</v>
       </c>
       <c r="B235" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C235" t="s">
         <v>16</v>
@@ -6456,13 +7172,16 @@
       <c r="D235" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E235" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>24</v>
       </c>
       <c r="B236" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C236" t="s">
         <v>16</v>
@@ -6470,13 +7189,16 @@
       <c r="D236" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E236" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>91</v>
       </c>
       <c r="B237" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C237" t="s">
         <v>16</v>
@@ -6484,13 +7206,16 @@
       <c r="D237" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E237" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>93</v>
       </c>
       <c r="B238" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C238" t="s">
         <v>16</v>
@@ -6498,13 +7223,16 @@
       <c r="D238" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E238" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>132</v>
       </c>
       <c r="B239" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C239" t="s">
         <v>16</v>
@@ -6512,13 +7240,16 @@
       <c r="D239" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E239" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>215</v>
       </c>
       <c r="B240" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C240" t="s">
         <v>16</v>
@@ -6526,13 +7257,16 @@
       <c r="D240" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E240" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>572</v>
       </c>
       <c r="B241" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C241" t="s">
         <v>16</v>
@@ -6540,13 +7274,16 @@
       <c r="D241" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E241" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>560</v>
       </c>
       <c r="B242" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C242" t="s">
         <v>561</v>
@@ -6554,13 +7291,16 @@
       <c r="D242" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E242" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>597</v>
       </c>
       <c r="B243" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C243" t="s">
         <v>561</v>
@@ -6568,13 +7308,16 @@
       <c r="D243" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E243" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>718</v>
       </c>
       <c r="B244" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C244" t="s">
         <v>561</v>
@@ -6582,13 +7325,16 @@
       <c r="D244" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E244" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>720</v>
       </c>
       <c r="B245" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C245" t="s">
         <v>561</v>
@@ -6596,13 +7342,16 @@
       <c r="D245" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E245" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>721</v>
       </c>
       <c r="B246" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C246" t="s">
         <v>561</v>
@@ -6610,13 +7359,16 @@
       <c r="D246" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E246" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>532</v>
       </c>
       <c r="B247" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C247" t="s">
         <v>533</v>
@@ -6624,13 +7376,22 @@
       <c r="D247" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E247" t="s">
+        <v>762</v>
+      </c>
+      <c r="F247" t="s">
+        <v>763</v>
+      </c>
+      <c r="G247" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>535</v>
       </c>
       <c r="B248" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C248" t="s">
         <v>533</v>
@@ -6638,13 +7399,22 @@
       <c r="D248" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E248" t="s">
+        <v>762</v>
+      </c>
+      <c r="F248" t="s">
+        <v>763</v>
+      </c>
+      <c r="G248" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>160</v>
       </c>
       <c r="B249" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C249" t="s">
         <v>161</v>
@@ -6652,13 +7422,16 @@
       <c r="D249" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E249" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>188</v>
       </c>
       <c r="B250" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C250" t="s">
         <v>161</v>
@@ -6666,13 +7439,16 @@
       <c r="D250" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E250" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>237</v>
       </c>
       <c r="B251" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C251" t="s">
         <v>161</v>
@@ -6680,13 +7456,16 @@
       <c r="D251" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E251" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>299</v>
       </c>
       <c r="B252" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C252" t="s">
         <v>161</v>
@@ -6694,13 +7473,16 @@
       <c r="D252" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E252" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>301</v>
       </c>
       <c r="B253" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C253" t="s">
         <v>161</v>
@@ -6708,13 +7490,16 @@
       <c r="D253" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E253" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>319</v>
       </c>
       <c r="B254" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C254" t="s">
         <v>161</v>
@@ -6722,13 +7507,16 @@
       <c r="D254" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E254" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>329</v>
       </c>
       <c r="B255" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C255" t="s">
         <v>161</v>
@@ -6736,13 +7524,16 @@
       <c r="D255" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E255" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>331</v>
       </c>
       <c r="B256" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C256" t="s">
         <v>161</v>
@@ -6750,13 +7541,16 @@
       <c r="D256" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E256" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>376</v>
       </c>
       <c r="B257" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C257" t="s">
         <v>161</v>
@@ -6764,13 +7558,16 @@
       <c r="D257" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E257" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>377</v>
       </c>
       <c r="B258" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C258" t="s">
         <v>161</v>
@@ -6778,13 +7575,16 @@
       <c r="D258" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E258" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>379</v>
       </c>
       <c r="B259" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C259" t="s">
         <v>161</v>
@@ -6792,13 +7592,16 @@
       <c r="D259" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E259" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>381</v>
       </c>
       <c r="B260" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C260" t="s">
         <v>161</v>
@@ -6806,13 +7609,16 @@
       <c r="D260" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E260" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>383</v>
       </c>
       <c r="B261" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C261" t="s">
         <v>161</v>
@@ -6820,13 +7626,16 @@
       <c r="D261" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E261" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>401</v>
       </c>
       <c r="B262" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C262" t="s">
         <v>161</v>
@@ -6834,13 +7643,16 @@
       <c r="D262" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E262" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>403</v>
       </c>
       <c r="B263" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C263" t="s">
         <v>161</v>
@@ -6848,13 +7660,16 @@
       <c r="D263" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E263" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>479</v>
       </c>
       <c r="B264" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C264" t="s">
         <v>161</v>
@@ -6862,13 +7677,16 @@
       <c r="D264" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E264" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>537</v>
       </c>
       <c r="B265" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C265" t="s">
         <v>161</v>
@@ -6876,13 +7694,16 @@
       <c r="D265" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E265" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>588</v>
       </c>
       <c r="B266" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C266" t="s">
         <v>161</v>
@@ -6890,13 +7711,16 @@
       <c r="D266" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E266" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>643</v>
       </c>
       <c r="B267" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C267" t="s">
         <v>161</v>
@@ -6904,13 +7728,16 @@
       <c r="D267" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E267" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>708</v>
       </c>
       <c r="B268" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C268" t="s">
         <v>161</v>
@@ -6918,13 +7745,16 @@
       <c r="D268" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E268" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>32</v>
       </c>
       <c r="B269" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C269" t="s">
         <v>33</v>
@@ -6932,13 +7762,22 @@
       <c r="D269" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E269" t="s">
+        <v>762</v>
+      </c>
+      <c r="F269" t="s">
+        <v>763</v>
+      </c>
+      <c r="G269" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>114</v>
       </c>
       <c r="B270" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C270" t="s">
         <v>33</v>
@@ -6946,13 +7785,22 @@
       <c r="D270" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E270" t="s">
+        <v>762</v>
+      </c>
+      <c r="F270" t="s">
+        <v>763</v>
+      </c>
+      <c r="G270" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>138</v>
       </c>
       <c r="B271" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C271" t="s">
         <v>33</v>
@@ -6960,13 +7808,22 @@
       <c r="D271" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E271" t="s">
+        <v>762</v>
+      </c>
+      <c r="F271" t="s">
+        <v>763</v>
+      </c>
+      <c r="G271" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>551</v>
       </c>
       <c r="B272" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C272" t="s">
         <v>33</v>
@@ -6974,13 +7831,22 @@
       <c r="D272" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E272" t="s">
+        <v>762</v>
+      </c>
+      <c r="F272" t="s">
+        <v>763</v>
+      </c>
+      <c r="G272" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>637</v>
       </c>
       <c r="B273" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C273" t="s">
         <v>33</v>
@@ -6988,13 +7854,22 @@
       <c r="D273" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E273" t="s">
+        <v>762</v>
+      </c>
+      <c r="F273" t="s">
+        <v>763</v>
+      </c>
+      <c r="G273" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>179</v>
       </c>
       <c r="B274" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C274" t="s">
         <v>180</v>
@@ -7002,13 +7877,16 @@
       <c r="D274" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E274" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>358</v>
       </c>
       <c r="B275" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C275" t="s">
         <v>180</v>
@@ -7016,13 +7894,16 @@
       <c r="D275" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E275" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>664</v>
       </c>
       <c r="B276" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C276" t="s">
         <v>180</v>
@@ -7030,13 +7911,16 @@
       <c r="D276" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E276" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>666</v>
       </c>
       <c r="B277" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C277" t="s">
         <v>180</v>
@@ -7044,13 +7928,16 @@
       <c r="D277" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E277" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>668</v>
       </c>
       <c r="B278" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C278" t="s">
         <v>180</v>
@@ -7058,13 +7945,16 @@
       <c r="D278" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E278" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>688</v>
       </c>
       <c r="B279" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C279" t="s">
         <v>180</v>
@@ -7072,13 +7962,16 @@
       <c r="D279" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E279" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C280" t="s">
         <v>1</v>
@@ -7086,13 +7979,16 @@
       <c r="D280" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E280" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>3</v>
       </c>
       <c r="B281" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C281" t="s">
         <v>1</v>
@@ -7100,13 +7996,16 @@
       <c r="D281" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E281" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>5</v>
       </c>
       <c r="B282" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C282" t="s">
         <v>1</v>
@@ -7114,13 +8013,16 @@
       <c r="D282" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E282" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>7</v>
       </c>
       <c r="B283" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C283" t="s">
         <v>1</v>
@@ -7128,13 +8030,16 @@
       <c r="D283" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E283" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>61</v>
       </c>
       <c r="B284" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C284" t="s">
         <v>1</v>
@@ -7142,13 +8047,16 @@
       <c r="D284" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E284" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>76</v>
       </c>
       <c r="B285" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C285" t="s">
         <v>1</v>
@@ -7156,13 +8064,16 @@
       <c r="D285" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E285" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>567</v>
       </c>
       <c r="B286" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C286" t="s">
         <v>1</v>
@@ -7170,13 +8081,16 @@
       <c r="D286" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E286" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>568</v>
       </c>
       <c r="B287" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C287" t="s">
         <v>1</v>
@@ -7184,13 +8098,16 @@
       <c r="D287" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E287" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C288" t="s">
         <v>10</v>
@@ -7198,13 +8115,16 @@
       <c r="D288" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E288" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>63</v>
       </c>
       <c r="B289" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C289" t="s">
         <v>10</v>
@@ -7212,13 +8132,16 @@
       <c r="D289" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E289" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>65</v>
       </c>
       <c r="B290" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C290" t="s">
         <v>10</v>
@@ -7226,13 +8149,16 @@
       <c r="D290" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E290" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>297</v>
       </c>
       <c r="B291" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C291" t="s">
         <v>10</v>
@@ -7240,13 +8166,16 @@
       <c r="D291" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E291" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>311</v>
       </c>
       <c r="B292" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C292" t="s">
         <v>10</v>
@@ -7254,13 +8183,16 @@
       <c r="D292" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E292" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>315</v>
       </c>
       <c r="B293" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C293" t="s">
         <v>10</v>
@@ -7268,13 +8200,16 @@
       <c r="D293" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E293" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>344</v>
       </c>
       <c r="B294" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C294" t="s">
         <v>10</v>
@@ -7282,13 +8217,16 @@
       <c r="D294" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E294" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>389</v>
       </c>
       <c r="B295" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C295" t="s">
         <v>10</v>
@@ -7296,13 +8234,16 @@
       <c r="D295" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E295" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>391</v>
       </c>
       <c r="B296" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C296" t="s">
         <v>10</v>
@@ -7310,13 +8251,16 @@
       <c r="D296" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E296" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>515</v>
       </c>
       <c r="B297" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C297" t="s">
         <v>10</v>
@@ -7324,13 +8268,16 @@
       <c r="D297" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E297" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>574</v>
       </c>
       <c r="B298" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C298" t="s">
         <v>10</v>
@@ -7338,13 +8285,16 @@
       <c r="D298" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E298" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>686</v>
       </c>
       <c r="B299" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C299" t="s">
         <v>10</v>
@@ -7352,13 +8302,16 @@
       <c r="D299" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E299" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>111</v>
       </c>
       <c r="B300" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C300" t="s">
         <v>112</v>
@@ -7366,13 +8319,16 @@
       <c r="D300" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E300" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>405</v>
       </c>
       <c r="B301" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C301" t="s">
         <v>112</v>
@@ -7380,13 +8336,16 @@
       <c r="D301" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E301" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>407</v>
       </c>
       <c r="B302" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C302" t="s">
         <v>112</v>
@@ -7394,13 +8353,16 @@
       <c r="D302" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E302" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>452</v>
       </c>
       <c r="B303" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C303" t="s">
         <v>112</v>
@@ -7408,13 +8370,16 @@
       <c r="D303" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E303" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>453</v>
       </c>
       <c r="B304" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C304" t="s">
         <v>112</v>
@@ -7422,13 +8387,16 @@
       <c r="D304" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E304" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>95</v>
       </c>
       <c r="B305" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C305" t="s">
         <v>96</v>
@@ -7436,13 +8404,16 @@
       <c r="D305" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E305" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>203</v>
       </c>
       <c r="B306" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C306" t="s">
         <v>96</v>
@@ -7450,13 +8421,16 @@
       <c r="D306" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E306" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>362</v>
       </c>
       <c r="B307" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C307" t="s">
         <v>96</v>
@@ -7464,13 +8438,16 @@
       <c r="D307" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E307" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>364</v>
       </c>
       <c r="B308" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C308" t="s">
         <v>96</v>
@@ -7478,13 +8455,16 @@
       <c r="D308" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E308" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>366</v>
       </c>
       <c r="B309" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C309" t="s">
         <v>96</v>
@@ -7492,13 +8472,16 @@
       <c r="D309" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E309" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>368</v>
       </c>
       <c r="B310" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C310" t="s">
         <v>96</v>
@@ -7506,13 +8489,16 @@
       <c r="D310" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E310" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>372</v>
       </c>
       <c r="B311" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C311" t="s">
         <v>96</v>
@@ -7520,13 +8506,16 @@
       <c r="D311" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E311" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>712</v>
       </c>
       <c r="B312" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C312" t="s">
         <v>96</v>
@@ -7534,13 +8523,16 @@
       <c r="D312" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E312" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>47</v>
       </c>
       <c r="B313" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C313" t="s">
         <v>48</v>
@@ -7548,13 +8540,16 @@
       <c r="D313" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E313" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>67</v>
       </c>
       <c r="B314" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C314" t="s">
         <v>48</v>
@@ -7562,13 +8557,16 @@
       <c r="D314" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E314" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>69</v>
       </c>
       <c r="B315" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C315" t="s">
         <v>48</v>
@@ -7576,13 +8574,16 @@
       <c r="D315" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E315" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>120</v>
       </c>
       <c r="B316" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C316" t="s">
         <v>48</v>
@@ -7590,13 +8591,16 @@
       <c r="D316" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E316" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>122</v>
       </c>
       <c r="B317" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C317" t="s">
         <v>48</v>
@@ -7604,13 +8608,16 @@
       <c r="D317" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E317" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>124</v>
       </c>
       <c r="B318" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C318" t="s">
         <v>48</v>
@@ -7618,13 +8625,16 @@
       <c r="D318" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E318" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>211</v>
       </c>
       <c r="B319" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C319" t="s">
         <v>48</v>
@@ -7632,13 +8642,16 @@
       <c r="D319" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E319" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>213</v>
       </c>
       <c r="B320" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C320" t="s">
         <v>48</v>
@@ -7646,13 +8659,16 @@
       <c r="D320" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E320" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>274</v>
       </c>
       <c r="B321" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C321" t="s">
         <v>48</v>
@@ -7660,13 +8676,16 @@
       <c r="D321" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E321" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>286</v>
       </c>
       <c r="B322" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C322" t="s">
         <v>48</v>
@@ -7674,13 +8693,16 @@
       <c r="D322" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E322" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>370</v>
       </c>
       <c r="B323" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C323" t="s">
         <v>48</v>
@@ -7688,13 +8710,16 @@
       <c r="D323" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E323" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>443</v>
       </c>
       <c r="B324" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C324" t="s">
         <v>48</v>
@@ -7702,13 +8727,16 @@
       <c r="D324" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E324" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>652</v>
       </c>
       <c r="B325" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C325" t="s">
         <v>48</v>
@@ -7716,13 +8744,16 @@
       <c r="D325" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E325" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>654</v>
       </c>
       <c r="B326" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C326" t="s">
         <v>48</v>
@@ -7730,13 +8761,16 @@
       <c r="D326" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E326" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>737</v>
       </c>
       <c r="B327" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C327" t="s">
         <v>48</v>
@@ -7744,13 +8778,16 @@
       <c r="D327" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E327" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>84</v>
       </c>
       <c r="B328" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C328" t="s">
         <v>85</v>
@@ -7758,13 +8795,16 @@
       <c r="D328" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E328" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>87</v>
       </c>
       <c r="B329" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C329" t="s">
         <v>85</v>
@@ -7772,13 +8812,16 @@
       <c r="D329" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E329" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>89</v>
       </c>
       <c r="B330" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C330" t="s">
         <v>85</v>
@@ -7786,13 +8829,16 @@
       <c r="D330" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E330" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>147</v>
       </c>
       <c r="B331" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C331" t="s">
         <v>85</v>
@@ -7800,13 +8846,16 @@
       <c r="D331" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E331" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>346</v>
       </c>
       <c r="B332" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C332" t="s">
         <v>85</v>
@@ -7814,13 +8863,16 @@
       <c r="D332" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E332" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>348</v>
       </c>
       <c r="B333" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C333" t="s">
         <v>85</v>
@@ -7828,13 +8880,16 @@
       <c r="D333" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E333" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>354</v>
       </c>
       <c r="B334" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C334" t="s">
         <v>85</v>
@@ -7842,13 +8897,16 @@
       <c r="D334" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E334" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>356</v>
       </c>
       <c r="B335" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C335" t="s">
         <v>85</v>
@@ -7856,13 +8914,16 @@
       <c r="D335" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E335" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>547</v>
       </c>
       <c r="B336" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C336" t="s">
         <v>85</v>
@@ -7870,13 +8931,16 @@
       <c r="D336" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E336" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>292</v>
       </c>
       <c r="B337" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C337" t="s">
         <v>293</v>
@@ -7884,13 +8948,16 @@
       <c r="D337" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E337" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>522</v>
       </c>
       <c r="B338" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C338" t="s">
         <v>293</v>
@@ -7898,13 +8965,16 @@
       <c r="D338" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E338" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>524</v>
       </c>
       <c r="B339" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C339" t="s">
         <v>293</v>
@@ -7912,13 +8982,16 @@
       <c r="D339" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E339" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>526</v>
       </c>
       <c r="B340" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C340" t="s">
         <v>293</v>
@@ -7926,13 +8999,16 @@
       <c r="D340" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E340" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>528</v>
       </c>
       <c r="B341" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C341" t="s">
         <v>293</v>
@@ -7940,13 +9016,16 @@
       <c r="D341" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E341" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>607</v>
       </c>
       <c r="B342" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C342" t="s">
         <v>608</v>
@@ -7954,13 +9033,16 @@
       <c r="D342" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E342" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>610</v>
       </c>
       <c r="B343" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C343" t="s">
         <v>608</v>
@@ -7968,13 +9050,16 @@
       <c r="D343" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E343" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>239</v>
       </c>
       <c r="B344" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C344" t="s">
         <v>240</v>
@@ -7982,13 +9067,16 @@
       <c r="D344" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E344" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>325</v>
       </c>
       <c r="B345" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C345" t="s">
         <v>240</v>
@@ -7996,13 +9084,16 @@
       <c r="D345" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E345" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>399</v>
       </c>
       <c r="B346" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C346" t="s">
         <v>240</v>
@@ -8010,13 +9101,16 @@
       <c r="D346" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E346" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>660</v>
       </c>
       <c r="B347" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C347" t="s">
         <v>240</v>
@@ -8024,13 +9118,16 @@
       <c r="D347" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E347" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>26</v>
       </c>
       <c r="B348" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C348" t="s">
         <v>27</v>
@@ -8038,13 +9135,16 @@
       <c r="D348" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E348" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>104</v>
       </c>
       <c r="B349" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C349" t="s">
         <v>27</v>
@@ -8052,13 +9152,16 @@
       <c r="D349" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E349" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>106</v>
       </c>
       <c r="B350" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C350" t="s">
         <v>27</v>
@@ -8066,13 +9169,16 @@
       <c r="D350" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E350" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>118</v>
       </c>
       <c r="B351" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C351" t="s">
         <v>27</v>
@@ -8080,13 +9186,16 @@
       <c r="D351" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E351" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>270</v>
       </c>
       <c r="B352" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C352" t="s">
         <v>27</v>
@@ -8094,13 +9203,16 @@
       <c r="D352" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E352" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>590</v>
       </c>
       <c r="B353" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C353" t="s">
         <v>27</v>
@@ -8108,13 +9220,16 @@
       <c r="D353" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E353" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>601</v>
       </c>
       <c r="B354" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C354" t="s">
         <v>27</v>
@@ -8122,13 +9237,16 @@
       <c r="D354" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E354" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>333</v>
       </c>
       <c r="B355" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C355" t="s">
         <v>334</v>
@@ -8136,13 +9254,16 @@
       <c r="D355" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E355" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>603</v>
       </c>
       <c r="B356" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C356" t="s">
         <v>334</v>
@@ -8150,13 +9271,16 @@
       <c r="D356" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E356" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>682</v>
       </c>
       <c r="B357" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C357" t="s">
         <v>334</v>
@@ -8164,13 +9288,16 @@
       <c r="D357" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E357" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>149</v>
       </c>
       <c r="B358" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C358" t="s">
         <v>150</v>
@@ -8178,13 +9305,16 @@
       <c r="D358" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E358" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>209</v>
       </c>
       <c r="B359" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C359" t="s">
         <v>150</v>
@@ -8192,13 +9322,16 @@
       <c r="D359" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E359" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>327</v>
       </c>
       <c r="B360" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C360" t="s">
         <v>150</v>
@@ -8206,13 +9339,16 @@
       <c r="D360" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E360" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>487</v>
       </c>
       <c r="B361" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C361" t="s">
         <v>150</v>
@@ -8220,13 +9356,16 @@
       <c r="D361" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E361" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>489</v>
       </c>
       <c r="B362" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C362" t="s">
         <v>150</v>
@@ -8234,13 +9373,16 @@
       <c r="D362" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E362" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>491</v>
       </c>
       <c r="B363" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C363" t="s">
         <v>150</v>
@@ -8248,13 +9390,16 @@
       <c r="D363" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E363" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>493</v>
       </c>
       <c r="B364" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C364" t="s">
         <v>150</v>
@@ -8262,13 +9407,16 @@
       <c r="D364" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E364" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>553</v>
       </c>
       <c r="B365" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C365" t="s">
         <v>150</v>
@@ -8276,13 +9424,16 @@
       <c r="D365" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E365" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>563</v>
       </c>
       <c r="B366" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C366" t="s">
         <v>150</v>
@@ -8290,13 +9441,16 @@
       <c r="D366" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E366" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>669</v>
       </c>
       <c r="B367" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C367" t="s">
         <v>150</v>
@@ -8304,13 +9458,16 @@
       <c r="D367" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E367" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>142</v>
       </c>
       <c r="B368" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C368" t="s">
         <v>143</v>
@@ -8318,13 +9475,16 @@
       <c r="D368" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E368" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>260</v>
       </c>
       <c r="B369" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C369" t="s">
         <v>143</v>
@@ -8332,13 +9492,16 @@
       <c r="D369" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E369" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>395</v>
       </c>
       <c r="B370" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C370" t="s">
         <v>143</v>
@@ -8346,13 +9509,16 @@
       <c r="D370" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E370" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>397</v>
       </c>
       <c r="B371" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C371" t="s">
         <v>143</v>
@@ -8360,8 +9526,11 @@
       <c r="D371" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E371" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>692</v>
       </c>
@@ -8371,10 +9540,18 @@
       <c r="D372" t="s">
         <v>694</v>
       </c>
+      <c r="E372" t="s">
+        <v>765</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H372" xr:uid="{6BAAEFF7-3956-CB4E-95CA-4544906C3B79}">
-    <sortState ref="A2:H372">
+  <autoFilter ref="A1:G372" xr:uid="{6BAAEFF7-3956-CB4E-95CA-4544906C3B79}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="01_utilities"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A2:G372">
       <sortCondition ref="B1:B372"/>
     </sortState>
   </autoFilter>
@@ -8401,42 +9578,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/function_inventory.xlsx
+++ b/evaluation/function_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabriela/Dropbox/PERSONAL/LLC/Oikobit LLC/projects/code-and-statistics-forestgeo/fgeo2/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D2ADA9-2791-8249-80EC-CFD5BE41BDD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30713185-D87C-6040-A662-099A4472E63D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3460" yWindow="980" windowWidth="31940" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3440" yWindow="980" windowWidth="31940" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="functions" sheetId="1" r:id="rId1"/>
@@ -3162,7 +3162,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G372"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -7108,7 +7107,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>15</v>
       </c>
@@ -7125,7 +7124,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -7142,7 +7141,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>20</v>
       </c>
@@ -7159,7 +7158,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>22</v>
       </c>
@@ -7176,7 +7175,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>24</v>
       </c>
@@ -7193,7 +7192,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>91</v>
       </c>
@@ -7210,7 +7209,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>93</v>
       </c>
@@ -7227,7 +7226,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>132</v>
       </c>
@@ -7244,7 +7243,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>215</v>
       </c>
@@ -7261,7 +7260,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>572</v>
       </c>
@@ -7278,7 +7277,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>560</v>
       </c>
@@ -7295,7 +7294,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>597</v>
       </c>
@@ -7312,7 +7311,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>718</v>
       </c>
@@ -7329,7 +7328,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>720</v>
       </c>
@@ -7346,7 +7345,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>721</v>
       </c>
@@ -7363,7 +7362,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>532</v>
       </c>
@@ -7386,7 +7385,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>535</v>
       </c>
@@ -7409,7 +7408,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>160</v>
       </c>
@@ -7426,7 +7425,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>188</v>
       </c>
@@ -7443,7 +7442,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>237</v>
       </c>
@@ -7460,7 +7459,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>299</v>
       </c>
@@ -7477,7 +7476,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>301</v>
       </c>
@@ -7494,7 +7493,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>319</v>
       </c>
@@ -7511,7 +7510,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>329</v>
       </c>
@@ -7528,7 +7527,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>331</v>
       </c>
@@ -7545,7 +7544,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>376</v>
       </c>
@@ -7562,7 +7561,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>377</v>
       </c>
@@ -7579,7 +7578,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>379</v>
       </c>
@@ -7596,7 +7595,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>381</v>
       </c>
@@ -7613,7 +7612,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>383</v>
       </c>
@@ -7630,7 +7629,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>401</v>
       </c>
@@ -7647,7 +7646,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>403</v>
       </c>
@@ -7664,7 +7663,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>479</v>
       </c>
@@ -7681,7 +7680,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>537</v>
       </c>
@@ -7698,7 +7697,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>588</v>
       </c>
@@ -7715,7 +7714,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>643</v>
       </c>
@@ -7732,7 +7731,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>708</v>
       </c>
@@ -7749,7 +7748,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>32</v>
       </c>
@@ -7772,7 +7771,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>114</v>
       </c>
@@ -7795,7 +7794,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>138</v>
       </c>
@@ -7818,7 +7817,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>551</v>
       </c>
@@ -7841,7 +7840,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>637</v>
       </c>
@@ -7864,7 +7863,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>179</v>
       </c>
@@ -7881,7 +7880,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>358</v>
       </c>
@@ -7898,7 +7897,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>664</v>
       </c>
@@ -7915,7 +7914,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>666</v>
       </c>
@@ -7932,7 +7931,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>668</v>
       </c>
@@ -7949,7 +7948,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>688</v>
       </c>
@@ -7966,7 +7965,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>0</v>
       </c>
@@ -7983,7 +7982,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>3</v>
       </c>
@@ -8000,7 +7999,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -8017,7 +8016,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>7</v>
       </c>
@@ -8034,7 +8033,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>61</v>
       </c>
@@ -8051,7 +8050,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>76</v>
       </c>
@@ -8068,7 +8067,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>567</v>
       </c>
@@ -8085,7 +8084,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>568</v>
       </c>
@@ -8102,7 +8101,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -8119,7 +8118,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>63</v>
       </c>
@@ -8136,7 +8135,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>65</v>
       </c>
@@ -8153,7 +8152,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>297</v>
       </c>
@@ -8170,7 +8169,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>311</v>
       </c>
@@ -8187,7 +8186,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>315</v>
       </c>
@@ -8204,7 +8203,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>344</v>
       </c>
@@ -8221,7 +8220,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>389</v>
       </c>
@@ -8238,7 +8237,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>391</v>
       </c>
@@ -8255,7 +8254,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>515</v>
       </c>
@@ -8272,7 +8271,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>574</v>
       </c>
@@ -8289,7 +8288,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>686</v>
       </c>
@@ -8306,7 +8305,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>111</v>
       </c>
@@ -8323,7 +8322,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>405</v>
       </c>
@@ -8340,7 +8339,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>407</v>
       </c>
@@ -8357,7 +8356,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>452</v>
       </c>
@@ -8374,7 +8373,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>453</v>
       </c>
@@ -8391,7 +8390,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>95</v>
       </c>
@@ -8408,7 +8407,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>203</v>
       </c>
@@ -8425,7 +8424,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>362</v>
       </c>
@@ -8442,7 +8441,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>364</v>
       </c>
@@ -8459,7 +8458,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>366</v>
       </c>
@@ -8476,7 +8475,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>368</v>
       </c>
@@ -8493,7 +8492,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>372</v>
       </c>
@@ -8510,7 +8509,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>712</v>
       </c>
@@ -8527,7 +8526,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>47</v>
       </c>
@@ -8544,7 +8543,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>67</v>
       </c>
@@ -8561,7 +8560,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>69</v>
       </c>
@@ -8578,7 +8577,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>120</v>
       </c>
@@ -8595,7 +8594,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>122</v>
       </c>
@@ -8612,7 +8611,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>124</v>
       </c>
@@ -8629,7 +8628,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>211</v>
       </c>
@@ -8646,7 +8645,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>213</v>
       </c>
@@ -8663,7 +8662,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>274</v>
       </c>
@@ -8680,7 +8679,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>286</v>
       </c>
@@ -8697,7 +8696,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>370</v>
       </c>
@@ -8714,7 +8713,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>443</v>
       </c>
@@ -8731,7 +8730,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>652</v>
       </c>
@@ -8748,7 +8747,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>654</v>
       </c>
@@ -8765,7 +8764,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>737</v>
       </c>
@@ -8782,7 +8781,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>84</v>
       </c>
@@ -8799,7 +8798,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>87</v>
       </c>
@@ -8816,7 +8815,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>89</v>
       </c>
@@ -8833,7 +8832,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>147</v>
       </c>
@@ -8850,7 +8849,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>346</v>
       </c>
@@ -8867,7 +8866,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>348</v>
       </c>
@@ -8884,7 +8883,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>354</v>
       </c>
@@ -8901,7 +8900,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>356</v>
       </c>
@@ -8918,7 +8917,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>547</v>
       </c>
@@ -8935,7 +8934,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>292</v>
       </c>
@@ -8952,7 +8951,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>522</v>
       </c>
@@ -8969,7 +8968,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>524</v>
       </c>
@@ -8986,7 +8985,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>526</v>
       </c>
@@ -9003,7 +9002,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>528</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>607</v>
       </c>
@@ -9037,7 +9036,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>610</v>
       </c>
@@ -9054,7 +9053,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>239</v>
       </c>
@@ -9071,7 +9070,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>325</v>
       </c>
@@ -9088,7 +9087,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>399</v>
       </c>
@@ -9105,7 +9104,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>660</v>
       </c>
@@ -9122,7 +9121,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>26</v>
       </c>
@@ -9139,7 +9138,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>104</v>
       </c>
@@ -9156,7 +9155,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>106</v>
       </c>
@@ -9173,7 +9172,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>118</v>
       </c>
@@ -9190,7 +9189,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>270</v>
       </c>
@@ -9207,7 +9206,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>590</v>
       </c>
@@ -9224,7 +9223,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>601</v>
       </c>
@@ -9241,7 +9240,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>333</v>
       </c>
@@ -9258,7 +9257,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>603</v>
       </c>
@@ -9275,7 +9274,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>682</v>
       </c>
@@ -9292,7 +9291,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>149</v>
       </c>
@@ -9309,7 +9308,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>209</v>
       </c>
@@ -9326,7 +9325,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>327</v>
       </c>
@@ -9343,7 +9342,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>487</v>
       </c>
@@ -9360,7 +9359,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>489</v>
       </c>
@@ -9377,7 +9376,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>491</v>
       </c>
@@ -9394,7 +9393,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>493</v>
       </c>
@@ -9411,7 +9410,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>553</v>
       </c>
@@ -9428,7 +9427,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>563</v>
       </c>
@@ -9445,7 +9444,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>669</v>
       </c>
@@ -9462,7 +9461,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>142</v>
       </c>
@@ -9479,7 +9478,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>260</v>
       </c>
@@ -9496,7 +9495,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>395</v>
       </c>
@@ -9513,7 +9512,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>397</v>
       </c>
@@ -9530,7 +9529,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>692</v>
       </c>
@@ -9546,11 +9545,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G372" xr:uid="{6BAAEFF7-3956-CB4E-95CA-4544906C3B79}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="01_utilities"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A2:G372">
       <sortCondition ref="B1:B372"/>
     </sortState>

--- a/evaluation/function_inventory.xlsx
+++ b/evaluation/function_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabriela/Dropbox/PERSONAL/LLC/Oikobit LLC/projects/code-and-statistics-forestgeo/fgeo2/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30713185-D87C-6040-A662-099A4472E63D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEFF6A2-8DCB-6B4A-B8AD-07BF05C0BCA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="980" windowWidth="31940" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2040" yWindow="980" windowWidth="33340" windowHeight="18520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="functions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="779">
   <si>
     <t>abund.manycensus</t>
   </si>
@@ -2322,6 +2322,45 @@
   </si>
   <si>
     <t>not evaluated</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>Would be covered by more general application of torus translation null models, see https://github.com/gabrielareto/fgeo2/issues/3</t>
+  </si>
+  <si>
+    <t>See quadrats.qmd for examples on how to identiify neighboring quadrats and make community summaries from them</t>
+  </si>
+  <si>
+    <t>quadrats.R</t>
+  </si>
+  <si>
+    <t>Trivial calculation of distances between centroids. See quadrats.qmd for examples on how to calculate distances between quadrats.</t>
+  </si>
+  <si>
+    <t>Trivial -- use expand.grid() in base R</t>
+  </si>
+  <si>
+    <t>All ways of splitting a plot, naming quadrats, transformations local &lt;-&gt; global coordinates, are handled in a more general way with fewer functions. See quadrats.qmd for use cases.</t>
+  </si>
+  <si>
+    <t>Edited so it depends on the new functions to handle quadrats.</t>
+  </si>
+  <si>
+    <t>Removed dependency on deprecated and trivial convert.rowcol()</t>
+  </si>
+  <si>
+    <t>The function is not used by anything else, does not seem relevant</t>
+  </si>
+  <si>
+    <t>Edited to remove dependency on the deprecated gxgy.to.index()</t>
+  </si>
+  <si>
+    <t>See quadrats.qmd for equivalent use cases</t>
+  </si>
+  <si>
+    <t>Minor functionality with obsolete dependencies, both internal and external. Nothing depends on it</t>
   </si>
 </sst>
 </file>
@@ -3996,7 +4035,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>309</v>
       </c>
@@ -4013,7 +4052,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>352</v>
       </c>
@@ -4027,10 +4066,16 @@
         <v>353</v>
       </c>
       <c r="E50" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+        <v>762</v>
+      </c>
+      <c r="F50" t="s">
+        <v>766</v>
+      </c>
+      <c r="G50" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>416</v>
       </c>
@@ -4047,7 +4092,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>431</v>
       </c>
@@ -4064,7 +4109,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>433</v>
       </c>
@@ -4081,7 +4126,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>434</v>
       </c>
@@ -4098,7 +4143,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>435</v>
       </c>
@@ -4115,7 +4160,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>437</v>
       </c>
@@ -4132,7 +4177,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>457</v>
       </c>
@@ -4149,7 +4194,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>461</v>
       </c>
@@ -4166,7 +4211,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>463</v>
       </c>
@@ -4183,7 +4228,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>465</v>
       </c>
@@ -4200,7 +4245,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>467</v>
       </c>
@@ -4217,7 +4262,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>469</v>
       </c>
@@ -4234,7 +4279,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>470</v>
       </c>
@@ -4251,7 +4296,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>472</v>
       </c>
@@ -7310,6 +7355,9 @@
       <c r="E243" t="s">
         <v>765</v>
       </c>
+      <c r="G243" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
@@ -7422,7 +7470,13 @@
         <v>162</v>
       </c>
       <c r="E249" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F249" t="s">
+        <v>769</v>
+      </c>
+      <c r="G249" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
@@ -7439,7 +7493,13 @@
         <v>189</v>
       </c>
       <c r="E250" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F250" t="s">
+        <v>766</v>
+      </c>
+      <c r="G250" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -7456,7 +7516,13 @@
         <v>238</v>
       </c>
       <c r="E251" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F251" t="s">
+        <v>766</v>
+      </c>
+      <c r="G251" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
@@ -7473,7 +7539,13 @@
         <v>300</v>
       </c>
       <c r="E252" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F252" t="s">
+        <v>766</v>
+      </c>
+      <c r="G252" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -7490,7 +7562,13 @@
         <v>302</v>
       </c>
       <c r="E253" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F253" t="s">
+        <v>766</v>
+      </c>
+      <c r="G253" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -7507,7 +7585,13 @@
         <v>320</v>
       </c>
       <c r="E254" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F254" t="s">
+        <v>766</v>
+      </c>
+      <c r="G254" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
@@ -7524,7 +7608,13 @@
         <v>330</v>
       </c>
       <c r="E255" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F255" t="s">
+        <v>769</v>
+      </c>
+      <c r="G255" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.2">
@@ -7541,7 +7631,13 @@
         <v>332</v>
       </c>
       <c r="E256" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F256" t="s">
+        <v>769</v>
+      </c>
+      <c r="G256" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
@@ -7558,7 +7654,13 @@
         <v>70</v>
       </c>
       <c r="E257" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F257" t="s">
+        <v>769</v>
+      </c>
+      <c r="G257" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -7575,7 +7677,13 @@
         <v>378</v>
       </c>
       <c r="E258" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F258" t="s">
+        <v>769</v>
+      </c>
+      <c r="G258" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
@@ -7592,7 +7700,13 @@
         <v>380</v>
       </c>
       <c r="E259" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F259" t="s">
+        <v>769</v>
+      </c>
+      <c r="G259" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
@@ -7609,7 +7723,13 @@
         <v>382</v>
       </c>
       <c r="E260" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F260" t="s">
+        <v>769</v>
+      </c>
+      <c r="G260" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
@@ -7626,7 +7746,13 @@
         <v>384</v>
       </c>
       <c r="E261" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F261" t="s">
+        <v>769</v>
+      </c>
+      <c r="G261" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
@@ -7643,7 +7769,13 @@
         <v>402</v>
       </c>
       <c r="E262" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F262" t="s">
+        <v>769</v>
+      </c>
+      <c r="G262" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
@@ -7660,7 +7792,13 @@
         <v>404</v>
       </c>
       <c r="E263" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F263" t="s">
+        <v>769</v>
+      </c>
+      <c r="G263" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
@@ -7677,7 +7815,13 @@
         <v>480</v>
       </c>
       <c r="E264" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F264" t="s">
+        <v>769</v>
+      </c>
+      <c r="G264" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
@@ -7694,7 +7838,13 @@
         <v>538</v>
       </c>
       <c r="E265" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F265" t="s">
+        <v>766</v>
+      </c>
+      <c r="G265" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
@@ -7711,7 +7861,13 @@
         <v>589</v>
       </c>
       <c r="E266" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F266" t="s">
+        <v>769</v>
+      </c>
+      <c r="G266" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
@@ -7728,7 +7884,13 @@
         <v>208</v>
       </c>
       <c r="E267" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F267" t="s">
+        <v>769</v>
+      </c>
+      <c r="G267" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
@@ -7745,7 +7907,13 @@
         <v>709</v>
       </c>
       <c r="E268" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F268" t="s">
+        <v>766</v>
+      </c>
+      <c r="G268" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
@@ -7928,7 +8096,13 @@
         <v>667</v>
       </c>
       <c r="E277" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F277" t="s">
+        <v>766</v>
+      </c>
+      <c r="G277" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.2">
@@ -8030,7 +8204,13 @@
         <v>8</v>
       </c>
       <c r="E283" t="s">
-        <v>765</v>
+        <v>762</v>
+      </c>
+      <c r="F283" t="s">
+        <v>766</v>
+      </c>
+      <c r="G283" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.2">
@@ -8934,7 +9114,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>292</v>
       </c>
@@ -8951,7 +9131,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>522</v>
       </c>
@@ -8968,7 +9148,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>524</v>
       </c>
@@ -8985,7 +9165,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>526</v>
       </c>
@@ -9002,7 +9182,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>528</v>
       </c>
@@ -9019,7 +9199,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>607</v>
       </c>
@@ -9036,7 +9216,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>610</v>
       </c>
@@ -9053,7 +9233,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>239</v>
       </c>
@@ -9070,7 +9250,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>325</v>
       </c>
@@ -9086,8 +9266,11 @@
       <c r="E345" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G345" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>399</v>
       </c>
@@ -9104,7 +9287,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>660</v>
       </c>
@@ -9121,7 +9304,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>26</v>
       </c>
@@ -9137,8 +9320,11 @@
       <c r="E348" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G348" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>104</v>
       </c>
@@ -9155,7 +9341,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>106</v>
       </c>
@@ -9172,7 +9358,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>118</v>
       </c>
@@ -9189,7 +9375,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>270</v>
       </c>
